--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/FILTRO AR.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/FILTRO AR.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E52"/>
+  <dimension ref="A1:D52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,11 +432,6 @@
           <t>QUANTIDADE</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>PREÇO</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -457,11 +452,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -482,11 +472,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -507,7 +492,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -528,7 +512,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -549,7 +532,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -570,7 +552,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -591,7 +572,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -612,7 +592,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -633,11 +612,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -658,11 +632,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -683,7 +652,6 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -704,7 +672,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -725,11 +692,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -750,7 +712,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -771,7 +732,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -788,7 +748,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -809,7 +768,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -830,7 +788,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -847,7 +804,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -868,7 +824,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -889,7 +844,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -910,7 +864,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -931,7 +884,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -952,7 +904,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -973,7 +924,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -994,7 +944,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1015,7 +964,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1036,7 +984,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1057,7 +1004,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1078,7 +1024,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1099,7 +1044,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1120,7 +1064,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1141,11 +1084,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1166,7 +1104,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1187,7 +1124,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1208,11 +1144,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1233,11 +1164,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1258,7 +1184,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1279,7 +1204,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1300,7 +1224,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1321,11 +1244,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1346,7 +1264,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1367,7 +1284,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1388,11 +1304,6 @@
           <t>9</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -1413,7 +1324,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1434,7 +1344,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1455,7 +1364,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -1476,7 +1384,6 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -1497,7 +1404,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -1518,7 +1424,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -1539,7 +1444,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
